--- a/reports/一级子公司B_利润表_2025-08.xlsx
+++ b/reports/一级子公司B_利润表_2025-08.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>53873888</v>
+        <v>71598699</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>0</v>
+        <v>15844238</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0</v>
+        <v>114425372</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0</v>
+        <v>224385</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0</v>
+        <v>1611992</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0</v>
+        <v>202391</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0</v>
+        <v>1451071</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0</v>
+        <v>168914</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0</v>
+        <v>1209417</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0</v>
+        <v>157741</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0</v>
+        <v>1128900</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0</v>
+        <v>90093</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0</v>
+        <v>645098</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0</v>
+        <v>67471</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0</v>
+        <v>483793</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>53873888</v>
+        <v>70687704</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0</v>
+        <v>14933243</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>8932831</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0</v>
+        <v>64473185</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0</v>
+        <v>1337429</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0</v>
+        <v>9669268</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>668045</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0</v>
+        <v>4834018</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0</v>
+        <v>4453809</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>0</v>
+        <v>32225015</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0</v>
+        <v>445859</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>0</v>
+        <v>3222587</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0</v>
+        <v>335036</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>0</v>
+        <v>2417192</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>559745</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>0</v>
+        <v>4029307</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0</v>
+        <v>448913</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>0</v>
+        <v>3224068</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>53794094</v>
+        <v>53984372</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>386897115</v>
+        <v>386961364</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>79794</v>
+        <v>80446</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>639975</v>
+        <v>640278</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1014042</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>7257268</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>675601</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>4838224</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>49464808</v>
+        <v>63890473</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>28064532</v>
+        <v>35963210</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>168852</v>
+        <v>8056128</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1208973</v>
+        <v>58035714</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>27895680</v>
+        <v>27907082</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>201506717</v>
+        <v>201473599</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1671471</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>12086336</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>534406</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>3867168</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>334064</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>2416873</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>401359</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>2900357</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>301623</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2175513</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>201576</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1450586</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>168395</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1209058</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1351215</v>
+        <v>1349926</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>9671826</v>
+        <v>9674257</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>44613</v>
+        <v>45055</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>322410</v>
+        <v>322522</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>2807033</v>
+        <v>2816716</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>20149208</v>
+        <v>20159201</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>16790544</v>
+        <v>16887346</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>120905302</v>
+        <v>120954973</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0</v>
+        <v>2809837</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>0</v>
+        <v>20157509</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>451484</v>
+        <v>450544</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>3600137</v>
+        <v>3600041</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>398091</v>
+        <v>399477</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3199909</v>
+        <v>3199450</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>30171</v>
+        <v>29892</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>240004</v>
+        <v>239923</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>134291</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1079546</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>292242</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2114835</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>89491</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>719722</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>67207</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>539857</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>112246</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>899918</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>420092</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>3022130</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>60160</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>480128</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>45208</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>360138</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>75434</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>600265</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>52811</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>420176</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>37688</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>300096</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>30097</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>240042</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>22520</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>179997</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>4409080</v>
+        <v>7794729</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>-133671</v>
+        <v>4989255</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>167092</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1208588</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>37275</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>299869</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>60314</v>
+        <v>59668</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>480011</v>
+        <v>479821</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>4348766</v>
+        <v>7902153</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>1810657</v>
+        <v>1796502</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>14399930</v>
+        <v>14399032</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>2538109</v>
+        <v>6105651</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>2538109</v>
+        <v>6105651</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>2538109</v>
+        <v>6105651</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>2538109</v>
+        <v>6105651</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>2538109</v>
+        <v>6105651</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
